--- a/shop-classifier-webapp/shop.xlsx
+++ b/shop-classifier-webapp/shop.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\cpi_admin\WorkWebAdmin\shop-classifier-webapp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{833DB2BA-8692-44CD-BD51-41C258810407}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E010ECC2-E37F-42D9-85F5-A51CAD11B108}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4035" yWindow="2250" windowWidth="21690" windowHeight="7350" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="52">
   <si>
     <t>Result</t>
   </si>
@@ -48,9 +48,6 @@
     <t>ร้านอื่นๆ</t>
   </si>
   <si>
-    <t>ร้านหน้าโลตัส, ปลาผา, WASH, Amazon, เอเมซอน, คาเฟ่, Cafe, ศูนย์อาหาร, อาหาร, ร้านยา, ขายยา, ข้าว, DRUG, เอเซ่เว่น</t>
-  </si>
-  <si>
     <t>ไทวัสดุ</t>
   </si>
   <si>
@@ -93,24 +90,6 @@
     <t>Tesco Lotus</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial, sans-serif"/>
-      </rPr>
-      <t>โลตัส, Lotus, Tesco, โลตัล, Lotus's,โลตัส, Lotus, Tesco, โลตัล,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial, sans-serif"/>
-      </rPr>
-      <t xml:space="preserve"> ไฮเปอร์</t>
-    </r>
-  </si>
-  <si>
     <t>Seven Eleven</t>
   </si>
   <si>
@@ -144,9 +123,6 @@
     <t>Lotus_gofresh</t>
   </si>
   <si>
-    <t>โลตัส, tesco, Tesco, โลตัล, Lotus,โลตัส, Lotus, Tesco, โลตัล</t>
-  </si>
-  <si>
     <t>เฟรซ, เฟรช, โก, exp, gofresh, โก้</t>
   </si>
   <si>
@@ -195,9 +171,6 @@
     <t>BigC_mini</t>
   </si>
   <si>
-    <t>Big C, บิ๊กซี, บิกซี, BigC</t>
-  </si>
-  <si>
     <t>มินิ, Mini, mini</t>
   </si>
   <si>
@@ -205,17 +178,29 @@
   </si>
   <si>
     <t>บิ๊กซี, บิกซี, Big C, Big-C,Big C, บิ๊กซี, บิกซี, Big-C, BigC</t>
+  </si>
+  <si>
+    <t>ร้านหน้าโลตัส, ปลาผา, WASH, Amazon, เอเมซอน, คาเฟ่, Cafe, ศูนย์อาหาร, อาหาร, ร้านยา, ขายยา, ข้าว, DRUG, เอเซ่เว่น, นราไฮเปอร์</t>
+  </si>
+  <si>
+    <t>โลตัส, Lotus, Tesco, โลตัล, Lotus's,โลตัส, Lotus, Tesco, โลตัล, ไฮเปอร์,โลตัส, tesco, Tesco, โลตัล, Lotus,โลตัส, Lotus, Tesco, โลตัล</t>
+  </si>
+  <si>
+    <t>ไปรษณีย์ไทย</t>
+  </si>
+  <si>
+    <t>ไปรษณีย์เอกชน</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Tahoma"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -233,20 +218,17 @@
       <family val="2"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Tahoma"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF1F1F1F"/>
-      <name val="Arial, sans-serif"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Arial, sans-serif"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -259,17 +241,17 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF5B9BD5"/>
-        <bgColor rgb="FF5B9BD5"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDDEBF7"/>
-        <bgColor rgb="FFDDEBF7"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -278,32 +260,92 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="medium">
         <color rgb="FF000000"/>
       </left>
-      <right style="thin">
+      <right style="medium">
         <color rgb="FF000000"/>
       </right>
-      <top style="thin">
+      <top style="medium">
         <color rgb="FF000000"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF9BC2E6"/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
       </left>
-      <right style="thin">
+      <right style="medium">
         <color rgb="FF000000"/>
       </right>
-      <top style="thin">
+      <top style="medium">
         <color rgb="FF000000"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
       </bottom>
       <diagonal/>
     </border>
@@ -311,28 +353,46 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -614,237 +674,260 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <dimension ref="A1:C27"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="101.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="101.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15">
+    <row r="1" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" s="5"/>
+    </row>
+    <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="3"/>
-    </row>
-    <row r="3" spans="1:3" ht="15">
-      <c r="A3" s="4" t="s">
+      <c r="B3" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="C3" s="8"/>
+    </row>
+    <row r="4" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="6"/>
-    </row>
-    <row r="4" spans="1:3" ht="15">
-      <c r="A4" s="2" t="s">
+      <c r="B4" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="5"/>
+    </row>
+    <row r="5" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="3"/>
-    </row>
-    <row r="5" spans="1:3" ht="15">
-      <c r="A5" s="4" t="s">
+      <c r="B5" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="C5" s="8"/>
+    </row>
+    <row r="6" spans="1:3" ht="30" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="5"/>
-    </row>
-    <row r="6" spans="1:3" ht="15">
-      <c r="A6" s="2" t="s">
+      <c r="B6" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="C6" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="3" t="s">
+    </row>
+    <row r="7" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="6" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" ht="15">
-      <c r="A7" s="4" t="s">
+      <c r="B7" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="C7" s="8"/>
+    </row>
+    <row r="8" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="5"/>
-    </row>
-    <row r="8" spans="1:3" ht="15">
-      <c r="A8" s="2" t="s">
+      <c r="B8" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="C8" s="5"/>
+    </row>
+    <row r="9" spans="1:3" ht="30" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="5"/>
+    </row>
+    <row r="10" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="8"/>
+    </row>
+    <row r="11" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="5"/>
+    </row>
+    <row r="12" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="8"/>
+    </row>
+    <row r="13" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="5"/>
+    </row>
+    <row r="14" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="3"/>
-    </row>
-    <row r="9" spans="1:3" ht="15">
-      <c r="A9" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" s="5"/>
-    </row>
-    <row r="10" spans="1:3" ht="15">
-      <c r="A10" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" s="3"/>
-    </row>
-    <row r="11" spans="1:3" ht="15">
-      <c r="A11" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" s="5"/>
-    </row>
-    <row r="12" spans="1:3" ht="15">
-      <c r="A12" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C12" s="7"/>
-    </row>
-    <row r="13" spans="1:3" ht="15">
-      <c r="A13" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C13" s="5"/>
-    </row>
-    <row r="14" spans="1:3" ht="15">
-      <c r="A14" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C14" s="3"/>
-    </row>
-    <row r="15" spans="1:3" ht="15">
-      <c r="A15" s="4" t="s">
+      <c r="B15" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="C15" s="8"/>
+    </row>
+    <row r="16" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B16" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C16" s="5"/>
+    </row>
+    <row r="17" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="6" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" ht="15">
-      <c r="A16" s="2" t="s">
+      <c r="B17" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="C17" s="8"/>
+    </row>
+    <row r="18" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C16" s="7"/>
-    </row>
-    <row r="17" spans="1:3" ht="15">
-      <c r="A17" s="4" t="s">
+      <c r="B18" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="C18" s="5"/>
+    </row>
+    <row r="19" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="C17" s="5"/>
-    </row>
-    <row r="18" spans="1:3" ht="15">
-      <c r="A18" s="2" t="s">
+      <c r="B19" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="C19" s="8"/>
+    </row>
+    <row r="20" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C18" s="7"/>
-    </row>
-    <row r="19" spans="1:3" ht="15">
-      <c r="A19" s="4" t="s">
+      <c r="B20" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="C20" s="5"/>
+    </row>
+    <row r="21" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="C19" s="5"/>
-    </row>
-    <row r="20" spans="1:3" ht="15">
-      <c r="A20" s="2" t="s">
+      <c r="B21" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="C21" s="8"/>
+    </row>
+    <row r="22" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C20" s="3"/>
-    </row>
-    <row r="21" spans="1:3" ht="15">
-      <c r="A21" s="4" t="s">
+      <c r="B22" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="C22" s="5"/>
+    </row>
+    <row r="23" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="C21" s="5"/>
-    </row>
-    <row r="22" spans="1:3" ht="15">
-      <c r="A22" s="2" t="s">
+      <c r="B23" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C23" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B22" s="3" t="s">
+    </row>
+    <row r="24" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C22" s="3"/>
-    </row>
-    <row r="23" spans="1:3" ht="15">
-      <c r="A23" s="4" t="s">
+      <c r="B24" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="15">
-      <c r="A24" s="2" t="s">
+      <c r="C24" s="5"/>
+    </row>
+    <row r="25" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B25" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C25" s="8"/>
+    </row>
+    <row r="26" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C24" s="3"/>
+      <c r="B26" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="C26" s="5"/>
+    </row>
+    <row r="27" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="13"/>
+      <c r="B27" s="13"/>
+      <c r="C27" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
